--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2018_maule.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2018_maule.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>28.81967329293788</v>
+      </c>
+      <c r="C2">
         <v>27.51709719712271</v>
-      </c>
-      <c r="C2">
-        <v>28.81967329293788</v>
       </c>
       <c r="D2">
         <v>3.634104254661584</v>
       </c>
       <c r="E2">
-        <v>17.60116772968146</v>
+        <v>18.43435373687097</v>
       </c>
       <c r="F2">
         <v>63.96447853344757</v>
       </c>
       <c r="G2">
-        <v>18.43435373687097</v>
+        <v>17.60116772968146</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>30.02294431353094</v>
+      </c>
+      <c r="C3">
         <v>23.69775517797346</v>
-      </c>
-      <c r="C3">
-        <v>30.02294431353094</v>
       </c>
       <c r="D3">
         <v>4.219808975533168</v>
       </c>
       <c r="E3">
-        <v>15.41611198515471</v>
+        <v>19.53084029206503</v>
       </c>
       <c r="F3">
         <v>65.05304772278026</v>
       </c>
       <c r="G3">
-        <v>19.53084029206503</v>
+        <v>15.41611198515471</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>25.33470648815654</v>
+      </c>
+      <c r="C4">
         <v>46.89323721249571</v>
-      </c>
-      <c r="C4">
-        <v>25.33470648815654</v>
       </c>
       <c r="D4">
         <v>2.132503660322108</v>
       </c>
       <c r="E4">
-        <v>27.22742674905322</v>
+        <v>14.70998604743871</v>
       </c>
       <c r="F4">
         <v>58.06258720350807</v>
       </c>
       <c r="G4">
-        <v>14.70998604743871</v>
+        <v>27.22742674905322</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>34.42694663167104</v>
+      </c>
+      <c r="C5">
         <v>32.02099737532809</v>
-      </c>
-      <c r="C5">
-        <v>34.42694663167104</v>
       </c>
       <c r="D5">
         <v>3.122950819672131</v>
       </c>
       <c r="E5">
-        <v>19.23784494086728</v>
+        <v>20.68331143232589</v>
       </c>
       <c r="F5">
         <v>60.07884362680683</v>
       </c>
       <c r="G5">
-        <v>20.68331143232589</v>
+        <v>19.23784494086728</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>37.2722155772884</v>
+      </c>
+      <c r="C6">
         <v>16.72764370646591</v>
-      </c>
-      <c r="C6">
-        <v>37.2722155772884</v>
       </c>
       <c r="D6">
         <v>5.978128286014721</v>
       </c>
       <c r="E6">
+        <v>24.20275950292398</v>
+      </c>
+      <c r="F6">
+        <v>64.93512426900585</v>
+      </c>
+      <c r="G6">
         <v>10.86211622807018</v>
-      </c>
-      <c r="F6">
-        <v>64.93512426900584</v>
-      </c>
-      <c r="G6">
-        <v>24.20275950292397</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>25.50894509561999</v>
+      </c>
+      <c r="C7">
         <v>32.06354102405922</v>
-      </c>
-      <c r="C7">
-        <v>25.50894509561999</v>
       </c>
       <c r="D7">
         <v>3.118807118807119</v>
       </c>
       <c r="E7">
-        <v>20.3484388763825</v>
+        <v>16.18870509934423</v>
       </c>
       <c r="F7">
         <v>63.46285602427327</v>
       </c>
       <c r="G7">
-        <v>16.18870509934423</v>
+        <v>20.3484388763825</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>20.67968185104845</v>
+      </c>
+      <c r="C8">
         <v>29.73246565437455</v>
-      </c>
-      <c r="C8">
-        <v>20.67968185104845</v>
       </c>
       <c r="D8">
         <v>3.363326848249027</v>
       </c>
       <c r="E8">
+        <v>13.74867801172964</v>
+      </c>
+      <c r="F8">
+        <v>66.48399192385348</v>
+      </c>
+      <c r="G8">
         <v>19.76733006441688</v>
-      </c>
-      <c r="F8">
-        <v>66.48399192385347</v>
-      </c>
-      <c r="G8">
-        <v>13.74867801172964</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>28.35181728340837</v>
+      </c>
+      <c r="C9">
         <v>30.19655210277809</v>
-      </c>
-      <c r="C9">
-        <v>28.35181728340837</v>
       </c>
       <c r="D9">
         <v>3.311636363636364</v>
       </c>
       <c r="E9">
-        <v>19.04564027979777</v>
+        <v>17.88212480088649</v>
       </c>
       <c r="F9">
         <v>63.07223491931575</v>
       </c>
       <c r="G9">
-        <v>17.88212480088649</v>
+        <v>19.04564027979777</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>30.18754847352464</v>
+      </c>
+      <c r="C10">
         <v>28.83028978354368</v>
-      </c>
-      <c r="C10">
-        <v>30.18754847352464</v>
       </c>
       <c r="D10">
         <v>3.468574223526534</v>
       </c>
       <c r="E10">
-        <v>18.13022369033631</v>
+        <v>18.98374975059303</v>
       </c>
       <c r="F10">
         <v>62.88602655907066</v>
       </c>
       <c r="G10">
-        <v>18.98374975059303</v>
+        <v>18.13022369033631</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>26.16658304064225</v>
+      </c>
+      <c r="C11">
         <v>26.94430506773708</v>
-      </c>
-      <c r="C11">
-        <v>26.16658304064225</v>
       </c>
       <c r="D11">
         <v>3.711359404096834</v>
       </c>
       <c r="E11">
-        <v>17.59790267081763</v>
+        <v>17.08995575946256</v>
       </c>
       <c r="F11">
         <v>65.31214156971981</v>
       </c>
       <c r="G11">
-        <v>17.08995575946256</v>
+        <v>17.59790267081763</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>29.76759953293909</v>
+      </c>
+      <c r="C12">
         <v>36.03148894496968</v>
-      </c>
-      <c r="C12">
-        <v>29.76759953293909</v>
       </c>
       <c r="D12">
         <v>2.775350198620113</v>
       </c>
       <c r="E12">
-        <v>21.7320187196147</v>
+        <v>17.95401881048662</v>
       </c>
       <c r="F12">
         <v>60.31396246989868</v>
       </c>
       <c r="G12">
-        <v>17.95401881048662</v>
+        <v>21.7320187196147</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>28.98759215968351</v>
+      </c>
+      <c r="C13">
         <v>35.55115986333393</v>
-      </c>
-      <c r="C13">
-        <v>28.98759215968351</v>
       </c>
       <c r="D13">
         <v>2.81284774911482</v>
       </c>
       <c r="E13">
-        <v>21.60655737704918</v>
+        <v>17.61748633879781</v>
       </c>
       <c r="F13">
         <v>60.775956284153</v>
       </c>
       <c r="G13">
-        <v>17.61748633879781</v>
+        <v>21.60655737704918</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>26.22384334805145</v>
+      </c>
+      <c r="C14">
         <v>36.3409483586101</v>
-      </c>
-      <c r="C14">
-        <v>26.22384334805145</v>
       </c>
       <c r="D14">
         <v>2.751716851558373</v>
       </c>
       <c r="E14">
-        <v>22.3547472838923</v>
+        <v>16.13131790269249</v>
       </c>
       <c r="F14">
         <v>61.51393481341521</v>
       </c>
       <c r="G14">
-        <v>16.13131790269249</v>
+        <v>22.3547472838923</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>28.43057806591032</v>
+      </c>
+      <c r="C15">
         <v>23.82688894034113</v>
-      </c>
-      <c r="C15">
-        <v>28.43057806591032</v>
       </c>
       <c r="D15">
         <v>4.196939023402705</v>
       </c>
       <c r="E15">
-        <v>15.64907745336578</v>
+        <v>18.67269870235199</v>
       </c>
       <c r="F15">
         <v>65.67822384428224</v>
       </c>
       <c r="G15">
-        <v>18.67269870235199</v>
+        <v>15.64907745336578</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>25.23560209424084</v>
+      </c>
+      <c r="C16">
         <v>37.12789827973074</v>
-      </c>
-      <c r="C16">
-        <v>25.23560209424084</v>
       </c>
       <c r="D16">
         <v>2.693392425463336</v>
       </c>
       <c r="E16">
-        <v>22.86714575271789</v>
+        <v>15.54265708494564</v>
       </c>
       <c r="F16">
         <v>61.59019716233646</v>
       </c>
       <c r="G16">
-        <v>15.54265708494564</v>
+        <v>22.86714575271789</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>27.72935779816514</v>
+      </c>
+      <c r="C17">
         <v>33.02752293577982</v>
-      </c>
-      <c r="C17">
-        <v>27.72935779816514</v>
       </c>
       <c r="D17">
         <v>3.027777777777778</v>
       </c>
       <c r="E17">
-        <v>20.545013554002</v>
+        <v>17.24925096304751</v>
       </c>
       <c r="F17">
         <v>62.20573548295049</v>
       </c>
       <c r="G17">
-        <v>17.24925096304751</v>
+        <v>20.545013554002</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>30.15177855041455</v>
+      </c>
+      <c r="C18">
         <v>28.19938486226264</v>
-      </c>
-      <c r="C18">
-        <v>30.15177855041455</v>
       </c>
       <c r="D18">
         <v>3.546176644931831</v>
       </c>
       <c r="E18">
-        <v>17.8081324156568</v>
+        <v>19.04108432208757</v>
       </c>
       <c r="F18">
         <v>63.15078326225563</v>
       </c>
       <c r="G18">
-        <v>19.04108432208757</v>
+        <v>17.8081324156568</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>30.29270559083165</v>
+      </c>
+      <c r="C19">
         <v>31.99628310360849</v>
-      </c>
-      <c r="C19">
-        <v>30.29270559083165</v>
       </c>
       <c r="D19">
         <v>3.125363020329138</v>
       </c>
       <c r="E19">
-        <v>19.71562171962974</v>
+        <v>18.66590323504151</v>
       </c>
       <c r="F19">
         <v>61.61847504532876</v>
       </c>
       <c r="G19">
-        <v>18.66590323504151</v>
+        <v>19.71562171962974</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>26.20613098796004</v>
+      </c>
+      <c r="C20">
         <v>25.50593459140978</v>
-      </c>
-      <c r="C20">
-        <v>26.20613098796004</v>
       </c>
       <c r="D20">
         <v>3.920656176765986</v>
       </c>
       <c r="E20">
-        <v>16.81206731581021</v>
+        <v>17.27359711825294</v>
       </c>
       <c r="F20">
         <v>65.91433556593684</v>
       </c>
       <c r="G20">
-        <v>17.27359711825294</v>
+        <v>16.81206731581021</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>26.39980747633563</v>
+      </c>
+      <c r="C21">
         <v>29.1432696935665</v>
-      </c>
-      <c r="C21">
-        <v>26.39980747633563</v>
       </c>
       <c r="D21">
         <v>3.431323974676576</v>
       </c>
       <c r="E21">
-        <v>18.73646209386282</v>
+        <v>16.97266632284683</v>
       </c>
       <c r="F21">
         <v>64.29087158329035</v>
       </c>
       <c r="G21">
-        <v>16.97266632284683</v>
+        <v>18.73646209386282</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>27.94264404643101</v>
+      </c>
+      <c r="C22">
         <v>27.89012027942644</v>
-      </c>
-      <c r="C22">
-        <v>27.94264404643101</v>
       </c>
       <c r="D22">
         <v>3.585499058380414</v>
       </c>
       <c r="E22">
-        <v>17.89746873841383</v>
+        <v>17.93117395261047</v>
       </c>
       <c r="F22">
         <v>64.1713573089757</v>
       </c>
       <c r="G22">
-        <v>17.93117395261047</v>
+        <v>17.89746873841383</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>27.07203718048025</v>
+      </c>
+      <c r="C23">
         <v>37.29666924864446</v>
-      </c>
-      <c r="C23">
-        <v>27.07203718048025</v>
       </c>
       <c r="D23">
         <v>2.681204569055036</v>
       </c>
       <c r="E23">
-        <v>22.69085768143261</v>
+        <v>16.47031102733271</v>
       </c>
       <c r="F23">
         <v>60.83883129123469</v>
       </c>
       <c r="G23">
-        <v>16.47031102733271</v>
+        <v>22.69085768143261</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>28.88511688912893</v>
+      </c>
+      <c r="C24">
         <v>27.6352133323046</v>
-      </c>
-      <c r="C24">
-        <v>28.88511688912893</v>
       </c>
       <c r="D24">
         <v>3.618571667876487</v>
       </c>
       <c r="E24">
-        <v>17.65598966805674</v>
+        <v>18.45454635079313</v>
       </c>
       <c r="F24">
         <v>63.88946398115012</v>
       </c>
       <c r="G24">
-        <v>18.45454635079313</v>
+        <v>17.65598966805674</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>31.23061795628168</v>
+      </c>
+      <c r="C25">
         <v>30.39104455033659</v>
-      </c>
-      <c r="C25">
-        <v>31.23061795628168</v>
       </c>
       <c r="D25">
         <v>3.290443006470881</v>
       </c>
       <c r="E25">
-        <v>18.80381879445901</v>
+        <v>19.32328715836766</v>
       </c>
       <c r="F25">
         <v>61.87289404717335</v>
       </c>
       <c r="G25">
-        <v>19.32328715836766</v>
+        <v>18.80381879445901</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>27.94263882346784</v>
+      </c>
+      <c r="C26">
         <v>29.88433558381745</v>
-      </c>
-      <c r="C26">
-        <v>27.94263882346784</v>
       </c>
       <c r="D26">
         <v>3.346234676007005</v>
       </c>
       <c r="E26">
-        <v>18.93487199893885</v>
+        <v>17.70460273245789</v>
       </c>
       <c r="F26">
         <v>63.36052526860326</v>
       </c>
       <c r="G26">
-        <v>17.70460273245789</v>
+        <v>18.93487199893885</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>30.75560348147577</v>
+      </c>
+      <c r="C27">
         <v>32.33459138873912</v>
-      </c>
-      <c r="C27">
-        <v>30.75560348147577</v>
       </c>
       <c r="D27">
         <v>3.092663172939495</v>
       </c>
       <c r="E27">
-        <v>19.82620194578257</v>
+        <v>18.85803343723434</v>
       </c>
       <c r="F27">
         <v>61.3157646169831</v>
       </c>
       <c r="G27">
-        <v>18.85803343723434</v>
+        <v>19.82620194578257</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>29.70525275810967</v>
+      </c>
+      <c r="C28">
         <v>32.36456446566771</v>
-      </c>
-      <c r="C28">
-        <v>29.70525275810967</v>
       </c>
       <c r="D28">
         <v>3.089799033324854</v>
       </c>
       <c r="E28">
-        <v>19.96951993903988</v>
+        <v>18.32867665735331</v>
       </c>
       <c r="F28">
         <v>61.7018034036068</v>
       </c>
       <c r="G28">
-        <v>18.32867665735331</v>
+        <v>19.96951993903988</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>29.68065972104388</v>
+      </c>
+      <c r="C29">
         <v>29.44649947398785</v>
-      </c>
-      <c r="C29">
-        <v>29.68065972104388</v>
       </c>
       <c r="D29">
         <v>3.395989397257117</v>
       </c>
       <c r="E29">
-        <v>18.50501172957987</v>
+        <v>18.65216464064833</v>
       </c>
       <c r="F29">
         <v>62.84282362977181</v>
       </c>
       <c r="G29">
-        <v>18.65216464064833</v>
+        <v>18.50501172957987</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>29.09983961507618</v>
+      </c>
+      <c r="C30">
         <v>34.00160384923817</v>
-      </c>
-      <c r="C30">
-        <v>29.09983961507618</v>
       </c>
       <c r="D30">
         <v>2.941037735849056</v>
       </c>
       <c r="E30">
-        <v>20.84690553745929</v>
+        <v>17.84155860119231</v>
       </c>
       <c r="F30">
         <v>61.31153586134842</v>
       </c>
       <c r="G30">
-        <v>17.84155860119231</v>
+        <v>20.84690553745929</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>31.63256025466121</v>
+      </c>
+      <c r="C31">
         <v>29.42246475670759</v>
-      </c>
-      <c r="C31">
-        <v>31.63256025466121</v>
       </c>
       <c r="D31">
         <v>3.398763523956724</v>
       </c>
       <c r="E31">
-        <v>18.26857917325503</v>
+        <v>19.64084029817032</v>
       </c>
       <c r="F31">
         <v>62.09058052857466</v>
       </c>
       <c r="G31">
-        <v>19.64084029817032</v>
+        <v>18.26857917325503</v>
       </c>
     </row>
   </sheetData>
